--- a/testdata/login_cases.xlsx
+++ b/testdata/login_cases.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="登录测试" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="登录测试(链式调用)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'登录测试'!$A$1:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'登录测试(链式调用)'!$A$1:$K$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +44,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="002c3e50"/>
         <bgColor rgb="002c3e50"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00d5f5e3"/>
+        <bgColor rgb="00d5f5e3"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,12 +71,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -438,18 +447,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="36" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +509,16 @@
           <t>category</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>extract_path</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>save_as</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -507,7 +528,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>正常登录-获取Token</t>
+          <t>【前置】正常登录-获取Token</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -537,6 +558,16 @@
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>smoke</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>accessToken</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>token</t>
         </is>
       </c>
     </row>
@@ -548,7 +579,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>缺少password字段</t>
+          <t>【前置】提取refreshToken</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -564,20 +595,30 @@
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>{"username":"emilys"}</t>
+          <t>{"username":"emilys","password":"emilyspass"}</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Username and password required</t>
+          <t>refreshToken</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>smoke</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>refreshToken</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>refresh_token</t>
         </is>
       </c>
     </row>
@@ -589,38 +630,40 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>缺少username字段</t>
+          <t>用token获取当前用户信息</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>/auth/login</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>{"password":"emilyspass"}</t>
-        </is>
-      </c>
+          <t>/auth/me</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>{"Authorization":"Bearer {{token}}"}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Username and password required</t>
+          <t>username;;email;;firstName</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>negative</t>
-        </is>
-      </c>
+          <t>smoke</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -630,7 +673,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>空请求体</t>
+          <t>用refresh_token刷新令牌</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -640,26 +683,36 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>/auth/login</t>
+          <t>/auth/refresh</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"refreshToken":"{{refresh_token}}","expiresInMins":30}</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Username and password required</t>
+          <t>accessToken;;refreshToken</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>smoke</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>accessToken</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>new_token</t>
         </is>
       </c>
     </row>
@@ -671,7 +724,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>错误密码</t>
+          <t>缺少password字段</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -687,7 +740,7 @@
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>{"username":"emilys","password":"wrongpass"}</t>
+          <t>{"username":"emilys"}</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
@@ -695,7 +748,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Invalid credentials</t>
+          <t>Username and password required</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -703,6 +756,8 @@
           <t>negative</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -712,7 +767,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>未注册用户</t>
+          <t>错误密码</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -728,7 +783,7 @@
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>{"username":"noexist","password":"anything"}</t>
+          <t>{"username":"emilys","password":"wrongpass"}</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
@@ -744,6 +799,8 @@
           <t>negative</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -753,7 +810,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>空用户名+空密码</t>
+          <t>未注册用户</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -769,7 +826,7 @@
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>{"username":"","password":""}</t>
+          <t>{"username":"noexist","password":"anything"}</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
@@ -777,7 +834,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Username and password required</t>
+          <t>Invalid credentials</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -785,6 +842,8 @@
           <t>negative</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -794,7 +853,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>验证Token是JWT格式</t>
+          <t>空请求体</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -810,22 +869,24 @@
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>{"username":"emilys","password":"emilyspass"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>accessToken;;refreshToken</t>
+          <t>Username and password required</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
-        </is>
-      </c>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -835,7 +896,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>验证响应结构完整性</t>
+          <t>验证返回结构完整性</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -867,9 +928,11 @@
           <t>structure</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I10"/>
+  <autoFilter ref="A1:K10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>